--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,25 +442,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>区块名</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>JOIN+值计算</t>
+          <t>JOIN+值计算(单列)</t>
         </is>
       </c>
     </row>
@@ -1021,43 +1021,231 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>销售额,销量</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>sum,sum</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>季度汇总</t>
+          <t>地区单价分析</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总销售额,总销量</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>总销售额/总销量=单价(万元/个)</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>多列组合计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>季度汇总</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>跳过任务演示</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>销售额_A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>销售额_A=销售额区间</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>客户数_A</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>销售额_A=500,1000,1500,2000</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>block合并-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>销售额_B</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>销售额_B=销售额区间</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>客户数_B</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>销售额_B=500,1000,1500,2000</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>block合并-B</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1081,14 +1269,17 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1160,6 +1351,21 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>数据源</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>HTML生成</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>HTML图表类型</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>文字内容</t>
         </is>
       </c>
     </row>
@@ -1193,6 +1399,13 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1200,61 +1413,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>目录</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>各地区销售汇总</t>
+          <t>目录</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>按地区汇总</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>各地区总销售额</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>销售额最高地区: {max_cat} ({max_val})</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1262,101 +1446,113 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>多维统计分析</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2图左右</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>地区多维统计</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>各地区销售额对比</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
+          <t>一、销售汇总分析</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售数据多维分析</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售汇总</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>各地区总销售额</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>销售额最高地区: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>pie</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>地区占比</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>销售额占比</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>各地区销售额占比</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -1365,38 +1561,38 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱分布</t>
+          <t>多维统计分析</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1图</t>
+          <t>2图左右</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱</t>
+          <t>地区多维统计</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>销售额区间</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>总销售额</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>销售额区间客户分布</t>
+          <t>各地区销售额对比</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1405,50 +1601,410 @@
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>共 {count} 个区间</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>分析结论与说明</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>左图右文</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>本报告由防护用例自动生成，用于验证PPT输出格式是否正常。</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>pie</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>地区占比</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>销售额占比</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售额占比</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>pie</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>销售额分箱分布</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>销售额分箱</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>销售额区间</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>销售额区间客户分布</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>共 {count} 个区间</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>分析结论与说明</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>左图右文</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>本报告由防护用例自动生成</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>本报告基于测试数据生成，覆盖以下特性：
+1. 透视分析（分组、交叉表、占比、分箱）
+2. 多种图表类型（柱状图、饼图、折线图）
+3. 配置化PPT生成
+4. 结论模板自动填充
+5. 目录/章节/结尾页
+6. X轴长标签自动旋转</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>销售额区间</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>客户数_A</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试(列A)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>验证行维度不同+映射相同=合并区块</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>章节</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>二、扩展测试</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>长标签与布局验证</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>城市销售长标签测试</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>城市销售</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>各城市销售额对比</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>销售额最高城市: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>结尾</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>谢谢</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>防护用例测试完成</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -1260,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1277,9 +1277,8 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1340,7 +1339,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>区块名</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1355,15 +1354,10 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>HTML生成</t>
+          <t>是否生成</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>HTML图表类型</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>文字内容</t>
         </is>
@@ -1405,7 +1399,6 @@
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1438,7 +1431,6 @@
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1475,7 +1467,6 @@
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1543,12 +1534,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1613,7 +1599,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
@@ -1659,12 +1644,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>pie</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1732,12 +1712,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1774,11 +1749,10 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr">
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>本报告基于测试数据生成，覆盖以下特性：
 1. 透视分析（分组、交叉表、占比、分箱）
@@ -1857,7 +1831,6 @@
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1894,7 +1867,6 @@
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1962,12 +1934,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2004,7 +1971,70 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>跳过测试页(不应生成)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>不应出现的图表</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -454,13 +454,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,35 +510,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>列映射</t>
+          <t>值映射</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>值映射</t>
+          <t>分箱</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>分箱</t>
+          <t>值计算</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>值计算</t>
+          <t>是否计算</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>是否计算</t>
+          <t>过滤条件</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>过滤条件</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>区块名</t>
         </is>
@@ -581,21 +575,20 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>总销售额</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>简单分组求和</t>
         </is>
@@ -637,21 +630,20 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>总销售额,平均销售额,客户数</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>多字段多聚合</t>
         </is>
@@ -700,14 +692,13 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>交叉表</t>
         </is>
@@ -749,21 +740,20 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>销售额占比</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>占比聚合</t>
         </is>
@@ -805,21 +795,20 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>客户占比</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>计数占比</t>
         </is>
@@ -861,25 +850,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
           <t>销售额=500,1000,1500,2000|销售额区间</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>分箱统计</t>
         </is>
@@ -921,25 +909,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>总销售额</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>地区 = '华东' OR 地区 = '华北'</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>地区 = '华东' OR 地区 = '华北'</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>过滤条件</t>
         </is>
@@ -981,25 +968,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>总销售额</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>/1000</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>/1000</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr">
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>JOIN+值计算(单列)</t>
         </is>
@@ -1041,25 +1027,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>总销售额,总销量</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>总销售额/总销量=单价(万元/个)</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>总销售额/总销量=单价(万元/个)</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>多列组合计算</t>
         </is>
@@ -1101,21 +1086,20 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>总销售额</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>跳过任务演示</t>
         </is>
@@ -1161,25 +1145,24 @@
           <t>销售额_A=销售额区间</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>客户数_A</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>客户数_A</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
           <t>销售额_A=500,1000,1500,2000</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>block合并-A</t>
         </is>
@@ -1225,25 +1208,24 @@
           <t>销售额_B=销售额区间</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>客户数_B</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>客户数_B</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
           <t>销售额_B=500,1000,1500,2000</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>block合并-B</t>
         </is>
@@ -1260,25 +1242,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1299,65 +1279,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>副标题</t>
+          <t>布局</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>布局</t>
+          <t>图表类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>图表类型</t>
+          <t>数据Sheet</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据Sheet</t>
+          <t>X轴</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>X轴</t>
+          <t>Y轴</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Y轴</t>
+          <t>图表标题</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>图表标题</t>
+          <t>区块名</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>颜色</t>
+          <t>结论模板</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>区块名</t>
+          <t>数据源</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>结论模板</t>
+          <t>是否生成</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>数据源</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>是否生成</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>文字内容</t>
         </is>
@@ -1375,14 +1345,10 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>销售数据分析报告
-防护用例</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>基础防护测试 | 全特性覆盖</t>
-        </is>
-      </c>
+防护用例|基础防护测试 | 全特性覆盖</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1391,14 +1357,12 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1423,14 +1387,12 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1443,14 +1405,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>一、销售汇总分析</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>各地区销售数据多维分析</t>
-        </is>
-      </c>
+          <t>一、销售汇总分析|各地区销售数据多维分析</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1459,14 +1417,12 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1482,59 +1438,53 @@
           <t>各地区销售汇总</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1图</t>
+          <t>column</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>按地区汇总</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>按地区汇总</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>总销售额</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
           <t>各地区总销售额</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>销售额最高地区: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>销售额最高地区: {max_cat} ({max_val})</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1550,101 +1500,89 @@
           <t>多维统计分析</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2图左右</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2图左右</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>地区多维统计</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>地区多维统计</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>总销售额</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>各地区销售额对比</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>pie</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>pie</t>
+          <t>地区占比</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>地区占比</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>销售额占比</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>销售额占比</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
           <t>各地区销售额占比</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1660,59 +1598,53 @@
           <t>销售额分箱分布</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1图</t>
+          <t>line</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>销售额分箱</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱</t>
+          <t>销售额区间</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>销售额区间</t>
+          <t>客户数</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>销售额区间客户分布</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>共 {count} 个区间</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>共 {count} 个区间</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1728,31 +1660,29 @@
           <t>分析结论与说明</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>左图右文</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>本报告由防护用例自动生成</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>本报告由防护用例自动生成</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>本报告基于测试数据生成，覆盖以下特性：
 1. 透视分析（分组、交叉表、占比、分箱）
@@ -1778,59 +1708,53 @@
           <t>block合并测试</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1图</t>
+          <t>column</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>block合并测试</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>block合并测试</t>
+          <t>销售额区间</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>销售额区间</t>
+          <t>客户数_A</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>客户数_A</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>block合并测试(列A)</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>验证行维度不同+映射相同=合并区块</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>验证行维度不同+映射相同=合并区块</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1843,14 +1767,10 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>二、扩展测试</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>长标签与布局验证</t>
-        </is>
-      </c>
+          <t>二、扩展测试|长标签与布局验证</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1859,14 +1779,12 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1882,59 +1800,53 @@
           <t>城市销售长标签测试</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1图</t>
+          <t>column</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>城市销售</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>城市销售</t>
+          <t>城市</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>城市</t>
+          <t>销售额</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>各城市销售额对比</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>销售额最高城市: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>销售额最高城市: {max_cat} ({max_val})</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1947,14 +1859,10 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>谢谢</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>防护用例测试完成</t>
-        </is>
-      </c>
+          <t>谢谢|防护用例测试完成</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1963,14 +1871,12 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1986,55 +1892,49 @@
           <t>跳过测试页(不应生成)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1图</t>
+          <t>column</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>按地区汇总</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>按地区汇总</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>总销售额</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>不应出现的图表</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1228,6 +1228,57 @@
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>block合并-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>销售额,客户数</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>sum,avg</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>无行维度汇总</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>总销售额,平均客户数</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>无行维度_横向一行</t>
         </is>
       </c>
     </row>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>block合并-A</t>
+          <t>block合并测试</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>block合并-B</t>
+          <t>block合并测试</t>
         </is>
       </c>
     </row>
@@ -1279,6 +1279,61 @@
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>无行维度_横向一行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>销量</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>简单分组求和</t>
         </is>
       </c>
     </row>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1337,6 +1337,116 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>历史标量</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>标量生产者</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>销量</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>地区销量</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>销量/总销售额=销量占比</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>标量消费者</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1348,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1368,120 +1478,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>主题</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>珊瑚活力</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>页码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>页面类型</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>页面标题</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>布局</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>图表类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>数据Sheet</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>X轴</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Y轴</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>图表标题</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>区块名</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>结论模板</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>数据源</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>是否生成</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>文字内容</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="3">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>封面</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>销售数据分析报告
 防护用例|基础防护测试 | 全特性覆盖</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>目录</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>目录</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -1502,16 +1594,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>章节</t>
+          <t>目录</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>一、销售汇总分析|各地区销售数据多维分析</t>
+          <t>目录</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -1532,59 +1624,27 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>各地区销售汇总</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>按地区汇总</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>各地区总销售额</t>
-        </is>
-      </c>
+          <t>一、销售汇总分析|各地区销售数据多维分析</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>销售额最高地区: {max_cat} ({max_val})</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1594,95 +1654,117 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售汇总</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>各地区总销售额</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>销售额最高地区: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>多维统计分析</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2图左右</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>地区多维统计</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>地区</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>总销售额</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>各地区销售额对比</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>pie</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>地区占比</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>销售额占比</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>各地区销售额占比</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1691,60 +1773,38 @@
       <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>销售额分箱分布</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>pie</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱</t>
+          <t>地区占比</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>销售额区间</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>销售额占比</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>销售额区间客户分布</t>
+          <t>各地区销售额占比</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>共 {count} 个区间</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1754,41 +1814,103 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>销售额分箱分布</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>销售额分箱</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>销售额区间</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>销售额区间客户分布</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>共 {count} 个区间</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>分析结论与说明</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>左图右文</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>本报告由防护用例自动生成</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>本报告基于测试数据生成，覆盖以下特性：
 1. 透视分析（分组、交叉表、占比、分箱）
@@ -1800,91 +1922,61 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>block合并测试</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>block合并测试</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>销售额区间</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>客户数_A</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>block合并测试(列A)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>验证行维度不同+映射相同=合并区块</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>章节</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>二、扩展测试|长标签与布局验证</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>block合并测试</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>销售额区间</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>客户数_A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>block合并测试(列A)</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>验证行维度不同+映射相同=合并区块</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1894,59 +1986,27 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>城市销售长标签测试</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>城市销售</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>各城市销售额对比</t>
-        </is>
-      </c>
+          <t>二、扩展测试|长标签与布局验证</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>销售额最高城市: {max_cat} ({max_val})</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1956,27 +2016,59 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>结尾</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>谢谢|防护用例测试完成</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>城市销售长标签测试</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>城市销售</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>各城市销售额对比</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>销售额最高城市: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1986,61 +2078,91 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>结尾</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>跳过测试页(不应生成)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>按地区汇总</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>不应出现的图表</t>
-        </is>
-      </c>
+          <t>谢谢|防护用例测试完成</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>跳过测试页(不应生成)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>不应出现的图表</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1447,6 +1447,226 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>城市销售</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>销售额,销量</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>城市散点数据</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>销售额,销量</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>散点图数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>产品销售额</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>环形图数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>季度趋势</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>面积图数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>销售额,销量</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>组合图数据</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>总销售额,总销量</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>组合图数据</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1458,18 +1678,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -2112,57 +2332,701 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>跳过测试页(不应生成)</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1图</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>按地区汇总</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>总销售额</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>不应出现的图表</t>
-        </is>
-      </c>
+          <t>三、高级图表与多布局测试|散点图 · 环形图 · 面积图 · 组合图 · 多图布局</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>季度趋势与地区对比</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2图上下</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>季度趋势</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>季度销售额趋势(面积图)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>组合图数据</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售额(柱状图)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>多维度数据一览</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4图</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售额</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>各地区销量</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>地区单价分析</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>地区销售额对比</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>华东华北汇总</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>华东华北对比</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>图表背景说明</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>上文下图</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>各地区销售额</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>布局说明：上方文字区域 + 下方图表区域
+此布局适合需要详细文字说明的图表展示。
+支持下结论模板自动填充统计值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>城市销售额与销量散点图</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>scatter</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>城市散点数据</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>销量</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>销售额 vs 销量(散点图)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>共 {count} 个城市</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>产品销售额分布环形图</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>doughnut</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>产品销售额</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>各产品销售额占比</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>季度销售额趋势面积图</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>季度趋势</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>季度销售额趋势</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>最高季度: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>地区销售组合图(柱+折线)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>组合图数据</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>销售额(柱) + 销量(折)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>销售额最高: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>结尾</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>谢谢|全特性防护用例测试完成</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>跳过测试页(不应生成)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>不应出现的图表</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1667,6 +1667,65 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>销售额,销量</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>地区均价分析</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>金额,数量</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>金额/数量=均价(万元/个)</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>多列组合_异名映射</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1678,7 +1737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1688,7 +1747,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
@@ -3028,6 +3087,68 @@
       </c>
       <c r="N28" s="2" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>地区均价异名映射</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>地区均价分析</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>均价(万元/个)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>各地区均价(异名映射)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>均价最高: {max_cat} ({max_val})</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1723,6 +1723,61 @@
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>多列组合_异名映射</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>报告图片</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>地区图片</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>图片路径</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>地区图片</t>
         </is>
       </c>
     </row>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -456,7 +456,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
@@ -1035,7 +1035,8 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>总销售额/总销量=单价(万元/个)</t>
+          <t xml:space="preserve">总销售额/总销量=单价(万元/个)
+</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1778,6 +1779,226 @@
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>地区图片</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>运营商</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>nunique</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>地区运营商数</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>运营商数</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>nunique聚合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>地区最小销售额</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>最小销售额</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>min聚合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>运营商</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>去重拼接|、</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>地区运营商拼接</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>运营商列表</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>去重拼接聚合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>基站分布</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>站点名称</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量GB</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>基站分布数据</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量GB</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>基站分布数据</t>
         </is>
       </c>
     </row>
@@ -1792,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1907,7 +2128,7 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>销售数据分析报告
-防护用例|基础防护测试 | 全特性覆盖</t>
+全特性综合用例|基础防护测试 | 全特性覆盖</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -2247,12 +2468,10 @@
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>本报告基于测试数据生成，覆盖以下特性：
-1. 透视分析（分组、交叉表、占比、分箱）
-2. 多种图表类型（柱状图、饼图、折线图）
-3. 配置化PPT生成
-4. 结论模板自动填充
-5. 目录/章节/结尾页
-6. X轴长标签自动旋转</t>
+1. 透视分析（分组、交叉表、占比、分箱、JOIN、nunique、min、去重拼接）
+2. 多种图表类型（柱/饼/折/面积/散点/环形/组合/地图/热力）
+3. 配置化PPT生成（6种布局+结论模板）
+4. HTML报告（ECharts交互+经纬度地图）</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2548,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>二、扩展测试|长标签与布局验证</t>
+          <t>二、扩展测试|长标签 · 多布局 · 高级图表</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -2416,12 +2635,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>结尾</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>谢谢|防护用例测试完成</t>
+          <t>三、高级图表|散点图 · 环形图 · 面积图 · 组合图</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -2446,23 +2665,51 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>章节</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>三、高级图表与多布局测试|散点图 · 环形图 · 面积图 · 组合图 · 多图布局</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>季度趋势与地区对比</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2图上下</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>季度趋势</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>季度销售额趋势(面积图)</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -2471,37 +2718,23 @@
       <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>季度趋势与地区对比</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2图上下</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>column</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>季度趋势</t>
+          <t>组合图数据</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2511,16 +2744,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>季度销售额趋势(面积图)</t>
+          <t>各地区销售额(柱状图)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -2529,10 +2758,24 @@
       <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>多维度数据一览</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4图</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>column</t>
@@ -2540,7 +2783,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>组合图数据</t>
+          <t>按地区汇总</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2555,12 +2798,16 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额(柱状图)</t>
+          <t>各地区销售额</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -2569,24 +2816,10 @@
       <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>多维度数据一览</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4图</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>column</t>
@@ -2604,21 +2837,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总销量</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额</t>
+          <t>各地区销量</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>透视结果</t>
-        </is>
-      </c>
+      <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -2633,12 +2862,12 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>按地区汇总</t>
+          <t>地区单价分析</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2648,12 +2877,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>总销量</t>
+          <t>总销售额</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>各地区销量</t>
+          <t>地区销售额对比</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2673,12 +2902,12 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>column</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>地区单价分析</t>
+          <t>华东华北汇总</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2693,7 +2922,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>地区销售额对比</t>
+          <t>华东华北对比</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2707,10 +2936,24 @@
       <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>图表背景说明</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>上文下图</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>column</t>
@@ -2718,7 +2961,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>华东华北汇总</t>
+          <t>按地区汇总</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2733,18 +2976,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>华东华北对比</t>
+          <t>各地区销售额</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>透视结果</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>布局说明：上方文字区域 + 下方图表区域
+此布局适合需要详细文字说明的图表展示。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2757,41 +3009,45 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>图表背景说明</t>
+          <t>城市销售额与销量散点图</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>上文下图</t>
+          <t>1图</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>scatter</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>按地区汇总</t>
+          <t>城市散点数据</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>销售额</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>销量</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额</t>
+          <t>销售额 vs 销量(散点图)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>共 {count} 个城市</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
@@ -2802,13 +3058,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>布局说明：上方文字区域 + 下方图表区域
-此布局适合需要详细文字说明的图表展示。
-支持下结论模板自动填充统计值。</t>
-        </is>
-      </c>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2821,7 +3071,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>城市销售额与销量散点图</t>
+          <t>产品销售额分布环形图</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2831,35 +3081,31 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>scatter</t>
+          <t>doughnut</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>城市散点数据</t>
+          <t>产品销售额</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>产品</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>销量</t>
+          <t>总销售额</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>销售额 vs 销量(散点图)</t>
+          <t>各产品销售额占比</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>共 {count} 个城市</t>
-        </is>
-      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
@@ -2883,7 +3129,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>产品销售额分布环形图</t>
+          <t>季度销售额趋势面积图</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2893,17 +3139,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>doughnut</t>
+          <t>area</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>产品销售额</t>
+          <t>季度趋势</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>季度</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2913,11 +3159,15 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>各产品销售额占比</t>
+          <t>季度销售额趋势</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>最高季度: {max_cat} ({max_val})</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
@@ -2941,7 +3191,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>季度销售额趋势面积图</t>
+          <t>地区销售组合图(柱+折线)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2951,17 +3201,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>季度趋势</t>
+          <t>组合图数据</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2971,13 +3221,13 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>季度销售额趋势</t>
+          <t>销售额(柱) + 销量(折)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>最高季度: {max_cat} ({max_val})</t>
+          <t>销售额最高: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3003,7 +3253,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>地区销售组合图(柱+折线)</t>
+          <t>地区均价异名映射</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3013,12 +3263,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>组合图数据</t>
+          <t>地区均价分析</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3028,18 +3278,18 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>均价(万元/个)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>销售额(柱) + 销量(折)</t>
+          <t>各地区均价(异名映射)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>销售额最高: {max_cat} ({max_val})</t>
+          <t>均价最高: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3060,12 +3310,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>结尾</t>
+          <t>章节</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>谢谢|全特性防护用例测试完成</t>
+          <t>四、地理可视化|散点地图 · 热力地图</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -3095,7 +3345,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>跳过测试页(不应生成)</t>
+          <t>全国基站分布散点地图</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3105,39 +3355,43 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>map</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>按地区汇总</t>
+          <t>基站分布</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>经度</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>纬度</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>不应出现的图表</t>
+          <t>基站分布(散点地图)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>共 {count} 个基站</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>透视结果</t>
+          <t>测试数据.xlsx</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
@@ -3153,7 +3407,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>地区均价异名映射</t>
+          <t>全国基站分布热力地图</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3163,46 +3417,130 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>heatmap</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>地区均价分析</t>
+          <t>基站分布</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>经度</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>纬度</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>基站分布(热力地图)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>结尾</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>谢谢|全特性综合用例测试完成</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>跳过测试页(不应生成)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>1图</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>按地区汇总</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
           <t>地区</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>均价(万元/个)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>各地区均价(异名映射)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>均价最高: {max_cat} ({max_val})</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>不应出现的图表</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>透视结果</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -450,8 +450,8 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -1969,12 +1969,12 @@
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>用户数,流量GB</t>
+          <t>用户数,流量GB,经度,纬度</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>sum,sum</t>
+          <t>sum,sum,max,max</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>用户数,流量GB</t>
+          <t>用户数,流量GB,经度,纬度</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -1999,6 +1999,336 @@
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>基站分布数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>网络KPI</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>地区,运营商</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量GB,接通率,时延ms</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum,avg,avg</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>网络KPI地区汇总</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>总用户数,总流量,平均接通率,平均时延</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>地区运营商KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>网络KPI</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>基站名称</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量GB,RSRP均值,时延ms</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum,avg,avg</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>基站性能汇总</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>总用户数,总流量,信号均值,时延均值</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>基站性能</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>网络KPI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量GB,接通率,掉线率</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum,avg,avg</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>月度趋势</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量,接通率,掉线率</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>月度KPI趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>网络KPI</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>运营商</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>用户数</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>地区运营商交叉</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>地区运营商交叉</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>网络KPI</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>流量GB</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>地区流量占比</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>流量占比</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>流量占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>基站分布</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量GB</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>sum,sum</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>基站分布汇总</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>用户数,流量</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>基站分布统计</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3690,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>基站分布</t>
+          <t>基站分布数据</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3386,7 +3716,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>测试数据.xlsx</t>
+          <t>透视结果</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3422,7 +3752,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>基站分布</t>
+          <t>基站分布数据</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3444,7 +3774,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>测试数据.xlsx</t>
+          <t>透视结果</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2329,6 +2329,100 @@
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>基站分布统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>地区|区域</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>销售额|总销售额</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>合并写法_行值映射</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>合并写法_行值映射</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>地区｜区域</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>销售额｜总销售额</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>全角写法_行值映射</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>全角写法_行值映射</t>
         </is>
       </c>
     </row>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -538,6 +538,11 @@
           <t>区块名</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>导出列</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -2423,6 +2428,120 @@
       <c r="O35" t="inlineStr">
         <is>
           <t>全角写法_行值映射</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>导出列_聚合后名</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>导出列_聚合后名</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>地区,销售额_求和</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>地区,销售额_求和</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>测试数据.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>销售额|总销售额</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>导出列_映射名</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>导出列_映射名</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>地区,总销售额</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>地区,总销售额</t>
         </is>
       </c>
     </row>

--- a/cases/00_防护用例/项目配置.xlsx
+++ b/cases/00_防护用例/项目配置.xlsx
@@ -442,23 +442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -538,11 +538,6 @@
           <t>区块名</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>导出列</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -555,7 +550,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -566,7 +561,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -582,7 +577,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -610,7 +605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -621,7 +616,7 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>销售额,销售额,客户数</t>
+          <t>小区下行速率,小区下行速率,连接用户数</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -637,7 +632,7 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>总销售额,平均销售额,客户数</t>
+          <t>总下行速率,平均下行速率,连接用户数</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -665,7 +660,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -675,12 +670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -690,7 +685,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>地区产品交叉</t>
+          <t>地区频段交叉</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -720,7 +715,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -731,7 +726,7 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,7 +742,7 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>销售额占比</t>
+          <t>下行速率占比</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -775,18 +770,18 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -796,13 +791,13 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>产品计数占比</t>
+          <t>频段计数占比</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>客户占比</t>
+          <t>连接占比</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -830,18 +825,18 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -851,18 +846,18 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱</t>
+          <t>速率分箱</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>销售额=500,1000,1500,2000|销售额区间</t>
+          <t>小区下行速率=500,1000,1500,2000|速率区间</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -889,7 +884,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -900,7 +895,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -910,13 +905,13 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>华东华北汇总</t>
+          <t>高PRB汇总</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -928,7 +923,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>地区 = '华东' OR 地区 = '华北'</t>
+          <t>PRB利用率 &gt; 0.5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -943,23 +938,23 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>测试数据.xlsx@销售明细 JOIN 测试数据.xlsx@产品目录 ON 产品=产品</t>
+          <t>测试数据.xlsx@基站明细 JOIN 测试数据.xlsx@频段目录 ON 频段=频段</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -969,13 +964,13 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>产品系列汇总</t>
+          <t>频段类型汇总</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1007,7 +1002,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1018,7 +1013,7 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>销售额,销量</t>
+          <t>小区下行速率,用户数</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1028,19 +1023,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>地区单价分析</t>
+          <t>地区单用户速率</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>总销售额,总销量</t>
+          <t>总下行速率,总用户数</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">总销售额/总销量=单价(万元/个)
+          <t xml:space="preserve">总下行速率/总用户数=单用户速率(Mbps/人)
 </t>
         </is>
       </c>
@@ -1067,18 +1062,18 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>扇区ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1088,13 +1083,13 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>季度汇总</t>
+          <t>扇区汇总</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1122,18 +1117,18 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>销售额_A</t>
+          <t>小区下行速率_A</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1148,17 +1143,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>销售额_A=销售额区间</t>
+          <t>小区下行速率_A=速率区间</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>客户数_A</t>
+          <t>连接用户数_A</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>销售额_A=500,1000,1500,2000</t>
+          <t>小区下行速率_A=500,1000,1500,2000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1185,18 +1180,18 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>销售额_B</t>
+          <t>小区下行速率_B</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1211,17 +1206,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>销售额_B=销售额区间</t>
+          <t>小区下行速率_B=速率区间</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>客户数_B</t>
+          <t>连接用户数_B</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>销售额_B=500,1000,1500,2000</t>
+          <t>小区下行速率_B=500,1000,1500,2000</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1248,14 +1243,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>销售额,客户数</t>
+          <t>小区下行速率,连接用户数</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1271,7 +1266,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>总销售额,平均客户数</t>
+          <t>总下行速率,平均连接用户数</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -1299,7 +1294,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1310,7 +1305,7 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>销量</t>
+          <t>用户数</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1326,7 +1321,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>总销量</t>
+          <t>总用户数</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1354,14 +1349,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1377,7 +1372,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1405,7 +1400,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1416,7 +1411,7 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>销量</t>
+          <t>用户数</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1432,13 +1427,13 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>地区销量</t>
+          <t>地区用户数</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>销量/总销售额=销量占比</t>
+          <t>用户数/总下行速率=用户速率比</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1464,7 +1459,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>城市销售</t>
+          <t>城市汇总</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1475,7 +1470,7 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>销售额,销量</t>
+          <t>下行速率,用户数</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1491,7 +1486,7 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>销售额,销量</t>
+          <t>下行速率,用户数</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -1519,18 +1514,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1540,13 +1535,13 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>产品销售额</t>
+          <t>频段下行速率</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -1574,18 +1569,18 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>扇区ID</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1595,13 +1590,13 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>季度趋势</t>
+          <t>扇区趋势</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1640,7 +1635,7 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>销售额,销量</t>
+          <t>小区下行速率,用户数</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1656,7 +1651,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>总销售额,总销量</t>
+          <t>总下行速率,总用户数</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1695,7 +1690,7 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>销售额,销量</t>
+          <t>小区下行速率,用户数</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1705,19 +1700,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>地区均价分析</t>
+          <t>地区单用户速率分析</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>金额,数量</t>
+          <t>速率,数量</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>金额/数量=均价(万元/个)</t>
+          <t>速率/数量=单用户速率(Mbps/人)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1743,7 +1738,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1798,7 +1793,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1853,7 +1848,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1864,7 +1859,7 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1874,13 +1869,13 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>地区最小销售额</t>
+          <t>地区最低速率</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>最小销售额</t>
+          <t>最低下行速率</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -1908,7 +1903,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2018,530 +2013,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>网络KPI</t>
+          <t>基站明细</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>地区,运营商</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n"/>
+          <t>地区,频段</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>用户数,流量GB,接通率,时延ms</t>
+          <t>小区下行速率</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>sum,sum,avg,avg</t>
+          <t>avg</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>网络KPI地区汇总</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n"/>
+          <t>多级分类数据</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>总用户数,总流量,平均接通率,平均时延</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
+          <t>平均下行速率</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>地区运营商KPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>网络KPI</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>基站名称</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>用户数,流量GB,RSRP均值,时延ms</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>sum,sum,avg,avg</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>基站性能汇总</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>总用户数,总流量,信号均值,时延均值</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>基站性能</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>网络KPI</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>用户数,流量GB,接通率,掉线率</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>sum,sum,avg,avg</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>月度趋势</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>用户数,流量,接通率,掉线率</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>月度KPI趋势</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>网络KPI</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>运营商</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>用户数</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>地区运营商交叉</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>地区运营商交叉</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>网络KPI</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>流量GB</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>地区流量占比</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>流量占比</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>流量占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>基站分布</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>用户数,流量GB</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>sum,sum</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>基站分布汇总</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>用户数,流量</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>基站分布统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>销售明细</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>地区|区域</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>销售额|总销售额</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>合并写法_行值映射</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>合并写法_行值映射</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>销售明细</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>地区｜区域</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>销售额｜总销售额</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>全角写法_行值映射</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>全角写法_行值映射</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>销售明细</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>导出列_聚合后名</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>导出列_聚合后名</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>地区,销售额_求和</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>地区,销售额_求和</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>测试数据.xlsx</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>销售明细</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>销售额|总销售额</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>sum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>导出列_映射名</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>导出列_映射名</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>地区,总销售额</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>地区,总销售额</t>
+          <t>多级分类数据</t>
         </is>
       </c>
     </row>
@@ -2565,9 +2077,9 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -2670,7 +2182,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>销售数据分析报告
+          <t>基站性能数据分析报告
 全特性综合用例|基础防护测试 | 全特性覆盖</t>
         </is>
       </c>
@@ -2731,7 +2243,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>一、销售汇总分析|各地区销售数据多维分析</t>
+          <t>一、基站性能汇总|各地区基站数据多维分析</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -2761,7 +2273,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>各地区销售汇总</t>
+          <t>各地区基站总下行速率</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2786,18 +2298,18 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>各地区总销售额</t>
+          <t>各地区总下行速率</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>销售额最高地区: {max_cat} ({max_val})</t>
+          <t>下行速率最高地区: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2848,12 +2360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额对比</t>
+          <t>各地区下行速率对比</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -2892,12 +2404,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>销售额占比</t>
+          <t>下行速率占比</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额占比</t>
+          <t>各地区下行速率占比</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -2921,7 +2433,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱分布</t>
+          <t>小区下行速率分箱分布</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2936,22 +2448,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>销售额分箱</t>
+          <t>速率分箱</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>销售额区间</t>
+          <t>速率区间</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>客户数</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>销售额区间客户分布</t>
+          <t>速率区间连接用户分布</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -3010,8 +2522,8 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>本报告基于测试数据生成，覆盖以下特性：
-1. 透视分析（分组、交叉表、占比、分箱、JOIN、nunique、min、去重拼接）
+          <t>本报告基于基站性能数据生成，覆盖以下特性：
+1. 透视分析（分组、交叉表、占比、分箱、JOIN、nunique、min、去重拼接、多级分类）
 2. 多种图表类型（柱/饼/折/面积/散点/环形/组合/地图/热力）
 3. 配置化PPT生成（6种布局+结论模板）
 4. HTML报告（ECharts交互+经纬度地图）</t>
@@ -3049,12 +2561,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>销售额区间</t>
+          <t>速率区间</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>客户数_A</t>
+          <t>连接用户数_A</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3091,7 +2603,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>二、扩展测试|长标签 · 多布局 · 高级图表</t>
+          <t>二、扩展测试|长标签 · 多布局 · 高级图表 · 多级分类</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -3121,7 +2633,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>城市销售长标签测试</t>
+          <t>城市下行速率长标签测试</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3136,7 +2648,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>城市销售</t>
+          <t>城市汇总</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3146,18 +2658,18 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>下行速率</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>各城市销售额对比</t>
+          <t>各城市下行速率对比</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>销售额最高城市: {max_cat} ({max_val})</t>
+          <t>下行速率最高城市: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3213,7 +2725,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>季度趋势与地区对比</t>
+          <t>扇区趋势与地区对比</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3228,22 +2740,22 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>季度趋势</t>
+          <t>扇区趋势</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>扇区ID</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>季度销售额趋势(面积图)</t>
+          <t>扇区下行速率趋势(面积图)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -3282,12 +2794,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额(柱状图)</t>
+          <t>各地区下行速率(柱状图)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -3336,12 +2848,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额</t>
+          <t>各地区下行速率</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -3380,12 +2892,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>总销量</t>
+          <t>总用户数</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>各地区销量</t>
+          <t>各地区用户数</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -3410,7 +2922,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>地区单价分析</t>
+          <t>地区单用户速率</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3420,12 +2932,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>地区销售额对比</t>
+          <t>地区下行速率对比</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -3450,7 +2962,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>华东华北汇总</t>
+          <t>高PRB汇总</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3460,12 +2972,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>华东华北对比</t>
+          <t>高PRB地区对比</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -3514,12 +3026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>各地区销售额</t>
+          <t>各地区下行速率</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -3552,7 +3064,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>城市销售额与销量散点图</t>
+          <t>城市下行速率与用户数散点图</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3572,17 +3084,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>下行速率</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>销量</t>
+          <t>用户数</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>销售额 vs 销量(散点图)</t>
+          <t>下行速率 vs 用户数(散点图)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -3614,7 +3126,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>产品销售额分布环形图</t>
+          <t>频段下行速率分布环形图</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3629,22 +3141,22 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>产品销售额</t>
+          <t>频段下行速率</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>各产品销售额占比</t>
+          <t>各频段下行速率占比</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -3672,7 +3184,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>季度销售额趋势面积图</t>
+          <t>扇区下行速率趋势面积图</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3687,28 +3199,28 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>季度趋势</t>
+          <t>扇区趋势</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>扇区ID</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>季度销售额趋势</t>
+          <t>扇区下行速率趋势</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>最高季度: {max_cat} ({max_val})</t>
+          <t>最高速率扇区: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3734,7 +3246,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>地区销售组合图(柱+折线)</t>
+          <t>地区性能组合图(柱+折线)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3759,18 +3271,18 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>销售额(柱) + 销量(折)</t>
+          <t>下行速率(柱) + 用户数(折)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>销售额最高: {max_cat} ({max_val})</t>
+          <t>下行速率最高: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3796,7 +3308,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>地区均价异名映射</t>
+          <t>地区单用户速率异名映射</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3811,7 +3323,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>地区均价分析</t>
+          <t>地区单用户速率分析</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3821,18 +3333,18 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>均价(万元/个)</t>
+          <t>单用户速率(Mbps/人)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>各地区均价(异名映射)</t>
+          <t>各地区单用户速率(异名映射)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>均价最高: {max_cat} ({max_val})</t>
+          <t>速率最高: {max_cat} ({max_val})</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4063,7 +3575,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>总销售额</t>
+          <t>总下行速率</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
